--- a/artfynd/A 43154-2024 artfynd.xlsx
+++ b/artfynd/A 43154-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150665</v>
+        <v>121150666</v>
       </c>
       <c r="B2" t="n">
-        <v>77982</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644784</v>
+        <v>644906</v>
       </c>
       <c r="R2" t="n">
-        <v>7223176</v>
+        <v>7223286</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150666</v>
+        <v>121150665</v>
       </c>
       <c r="B3" t="n">
-        <v>91963</v>
+        <v>77985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644906</v>
+        <v>644784</v>
       </c>
       <c r="R3" t="n">
-        <v>7223286</v>
+        <v>7223176</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 43154-2024 artfynd.xlsx
+++ b/artfynd/A 43154-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150666</v>
+        <v>121150665</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>77988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644906</v>
+        <v>644784</v>
       </c>
       <c r="R2" t="n">
-        <v>7223286</v>
+        <v>7223176</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150665</v>
+        <v>121150666</v>
       </c>
       <c r="B3" t="n">
-        <v>77985</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644784</v>
+        <v>644906</v>
       </c>
       <c r="R3" t="n">
-        <v>7223176</v>
+        <v>7223286</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 43154-2024 artfynd.xlsx
+++ b/artfynd/A 43154-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150665</v>
+        <v>121150666</v>
       </c>
       <c r="B2" t="n">
-        <v>77988</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644784</v>
+        <v>644906</v>
       </c>
       <c r="R2" t="n">
-        <v>7223176</v>
+        <v>7223286</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150666</v>
+        <v>121150665</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>77988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644906</v>
+        <v>644784</v>
       </c>
       <c r="R3" t="n">
-        <v>7223286</v>
+        <v>7223176</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 43154-2024 artfynd.xlsx
+++ b/artfynd/A 43154-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150666</v>
+        <v>121150665</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>77991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644906</v>
+        <v>644784</v>
       </c>
       <c r="R2" t="n">
-        <v>7223286</v>
+        <v>7223176</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150665</v>
+        <v>121150666</v>
       </c>
       <c r="B3" t="n">
-        <v>77988</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644784</v>
+        <v>644906</v>
       </c>
       <c r="R3" t="n">
-        <v>7223176</v>
+        <v>7223286</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
